--- a/samples/ss_ngimbang_ingest.xlsx
+++ b/samples/ss_ngimbang_ingest.xlsx
@@ -631,31 +631,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -702,15 +692,11 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -726,7 +712,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -773,15 +758,11 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -797,7 +778,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -826,31 +806,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -879,31 +849,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -932,31 +892,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -985,31 +935,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1038,31 +978,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1091,31 +1021,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1144,19 +1064,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1172,7 +1084,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1201,31 +1112,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1254,35 +1155,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>bus A/B</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1311,19 +1203,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1339,7 +1223,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1368,31 +1251,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1421,35 +1294,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>aset milik KTT</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Milik Pelanggan</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1478,31 +1342,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1531,23 +1385,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>seksi A belum energize</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1563,7 +1410,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1592,19 +1438,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1620,7 +1458,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1649,19 +1486,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1677,7 +1506,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1724,31 +1552,26 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>IBT 150/70 kV</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1777,31 +1600,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1830,19 +1643,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1858,7 +1663,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1887,31 +1691,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1940,31 +1734,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1993,17 +1777,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>batas ke UP2B Jateng (SS Tanjung Jati 1,2 - Ungaran 3)</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -2019,13 +1797,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2054,17 +1830,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>aset milik KTT</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Milik Pelanggan</t>
@@ -2080,13 +1850,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2115,17 +1883,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>aset milik KTT</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Milik Pelanggan</t>
@@ -2141,13 +1903,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2254,7 +2014,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Outlet PLTU Tuban Jawa</t>
@@ -2275,7 +2034,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -2289,8 +2047,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2307,13 +2063,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>SUTT Ngimbang - Jatidondong</t>
@@ -2334,7 +2088,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -2348,8 +2101,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2366,13 +2117,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>SUTT Ngimbang - Babat</t>
@@ -2393,7 +2142,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -2407,8 +2155,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2425,13 +2171,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>SUTT Ngimbang - Merakurak</t>
@@ -2452,7 +2196,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -2466,8 +2209,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2484,7 +2225,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2515,7 +2255,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -2529,8 +2268,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2547,13 +2284,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>SUTT Tuban Jawa - Merakurak</t>
@@ -2574,7 +2309,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -2588,8 +2322,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2606,13 +2338,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>SUTT Jatidondong - Cendang</t>
@@ -2633,7 +2363,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -2647,8 +2376,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2665,13 +2392,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>SUTT Ngimbang - Jombang</t>
@@ -2692,7 +2417,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -2706,8 +2430,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2724,7 +2446,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2755,7 +2476,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -2769,8 +2489,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2787,13 +2505,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>SUTT Babat - Lamongan</t>
@@ -2814,7 +2530,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -2828,8 +2543,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2846,13 +2559,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>SUTT Merakurak - Holcim (aset milik KTT)</t>
@@ -2873,7 +2584,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>1</v>
       </c>
@@ -2887,8 +2597,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2905,13 +2613,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>SUTT Tuban - Kerek</t>
@@ -2932,7 +2638,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -2946,8 +2651,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2964,13 +2667,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>SUTT Bojonegoro - Cepu (arah UP2B Jateng)</t>
@@ -2991,7 +2692,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -3005,8 +2705,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3023,7 +2721,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3054,7 +2751,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -3068,8 +2764,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3086,7 +2780,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3117,7 +2810,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -3131,8 +2823,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3149,13 +2839,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>SUTT Kerek - Semen Tuban (aset milik KTT)</t>
@@ -3176,7 +2864,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>1</v>
       </c>
@@ -3190,8 +2877,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3208,13 +2893,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>SUTT Tuban - Tuban III (aset milik KTT)</t>
@@ -3235,7 +2918,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>1</v>
       </c>
@@ -3249,8 +2931,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3267,7 +2947,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3298,7 +2977,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -3312,8 +2990,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3330,7 +3006,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3361,7 +3036,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -3375,8 +3049,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3393,13 +3065,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>SUTT 70 kV Sungai Gemadu - Brata</t>
@@ -3420,7 +3090,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -3434,8 +3103,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3452,13 +3119,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>SUTT 70 kV Sungai Gemadu - Samsik</t>
@@ -3479,7 +3144,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -3493,8 +3157,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3511,7 +3173,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3585,17 +3246,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1. Berpotensi padam beban pada Subsistem tersebut. 2. Kesulitan dalam melakukan pemeliharaan IBT apabila bersamaan dengan outage pembangkit PLTU Tanjung Awar- awar2 unit</t>
+          <t>1. Berpotensi padam beban pada Subsistem tersebut. 2. Kesulitan dalam melakukan pemeliharaan IBT apabila bersamaan dengan outage pembangkit PLTU Tanjung Awar- awar 2 unit</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS IBT Ngimbang dengan total target sebesar485 MW. (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah atau menyesuaikan kondisi pembangkitan</t>
+          <t>1. Sudah terpasang OLS IBT Ngimbang dengan total target sebesar 485 MW. (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah atau menyesuaikan kondisi pembangkitan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1. Pembangunan PLTS 150 kV - 50 MW di Bojonegoro (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Penambahan Ext. IBT #3 GITET 500 kV Ngimbang. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025) informasi terupdate COD Juli 2026. 3. Pembangunan GITET 500 kV Tanjung Awar awar dan Line Bay terkait. (Berdasarkan Usulan / Solusi RUPTL 2025 - 2034, COD Tahun 2028). 4. Penambahan Ext. IBT #4 GITET 500 kV Ngimbang. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). Jangka Menengah: 5. Pembangunan PLTB 150 kV dengan Total 200 MW Tahap I di Tuban (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang : 6. Pembangunan PLTB 150 kV dengan Total 100 MW Tahap II di Tuban (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032)</t>
+          <t>Jangka Pendek: 1. Pembangunan PLTS 150 kV - 50 MW di Bojonegoro (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Penambahan Ext. IBT #3 GITET 500 kV Ngimbang. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025) informasi terupdate COD Juli 2026. 3. Pembangunan GITET 500 kV Tanjung Awar awar dan Line Bay terkait. (Berdasarkan Usulan / Solusi RUPTL 2025 - 2034, COD Tahun 2028). 4. Penambahan Ext. IBT #4 GITET 500 kV Ngimbang. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). Jangka Menengah : 5. Pembangunan PLTB 150 kV dengan Total 200 MW Tahap I di Tuban (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang : 6. Pembangunan PLTB 150 kV dengan Total 100 MW Tahap II di Tuban (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032)</t>
         </is>
       </c>
     </row>
@@ -3625,12 +3286,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS SUTT Babat- Bojonegoro dengan total target sebesar41MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS SUTT Babat- Bojonegoro dengan total target sebesar 41MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1. Usulan rekonduktoring SUTT 150 kV Babat-Bojonegoro dari kapasitas 580 A menjadi 2cct, HTLSC 1250 A per sirkit (COD dibutuhkan di 2026). 2. Pembangunan PLTS 150 kV - 50 MW di Bojonegoro (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026)</t>
+          <t>Jangka Pendek: 1. Usulan rekonduktoring SUTT 150 kV Babat-Bojonegoro dari kapasitas 580 A menjadi 2cct, HTLSC 1250 A per sirkit (COD dibutuhkan di 2026). 2. Pembangunan PLTS 150 kV - 50 MW di Bojonegoro (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026)</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3311,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] Busbar GI150 kVCerme dioperasikanSplit Busbar</t>
+          <t>[BELUM_DITETAPKAN] Busbar GI 150 kV Cerme dioperasikan Split Busbar</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3665,7 +3326,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Penambahan Bus Section di GI 150 kV Cerme. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026)</t>
+          <t>Jangka Pendek : Penambahan Bus Section di GI 150 kV Cerme. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026)</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3356,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.Pengaturan pekerjaan SUTT 150 kV Kerek-Tuban dan SUTT 150 kV Babat- Tanjung Awar-Awar tidak boleh bersamaan. 2.Perlu melakukan management beban pada PLTU Tanjung Awar-Awar saat pekerjaan SUTT 150 kVKerek-Tuban</t>
+          <t>1. Pengaturan pekerjaan SUTT 150 kV Kerek-Tuban dan SUTT 150 kV Babat- Tanjung Awar-Awar tidak boleh bersamaan. 2. Perlu melakukan management beban pada PLTU Tanjung Awar-Awar saat pekerjaan SUTT 150 kV Kerek-Tuban</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan proyek looping utara SUTT 150 kV Tuban- Paciran-Bungah-Manyar. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2.Rekonduktoring SUTT 150 kV Tuban-Kerek. (Berdasarkan RUPTL 2025-2034, COD Tahun 2026). 3.Rekonduktoring SUTT 150 kV Kerek-Mliwang. (Berdasarkan Usulan / Solusi RUPTL 2025-2034, COD Tahun 2028)</t>
+          <t>Jangka Pendek : 1. Pembangunan proyek looping utara SUTT 150 kV Tuban- Paciran-Bungah-Manyar. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Rekonduktoring SUTT 150 kV Tuban-Kerek. (Berdasarkan RUPTL 2025 -2034, COD Tahun 2026). 3. Rekonduktoring SUTT 150 kV Kerek-Mliwang. (Berdasarkan Usulan / Solusi RUPTL 2025 -2034, COD Tahun 2028)</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3396,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1. Usulanpemindahanleveltega nganpelangganKTT Semen Gresik dan Barata dari70 kVke150kV(diusulkanCOD Tahun2026). 2. Extension IBT ke-2 150/70kV di GI Segoromadu. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026)</t>
+          <t>Jangka Pendek : 1. Usulanpemindahanleveltega nganpelangganKTT Semen Gresik dan Barata dari 70 kV ke150kV(diusulkanCOD Tahun 2026). 2. Extension IBT ke-2 150/70kV di GI Segoromadu. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026)</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3431,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1. Pembangunan proyek looping utara SUTT 150 kV Bungah- Paciran. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 3. Pembangunan SUTET 500 kV Krian - Waru. (BerdasarkanRUPTL 2025 - 2034,CODTahun2025, MundurCOD 2028). 4. Usulan pemasangan Kapasitor sebesar 50 MVAR di GI Petrokimia COD Tahun 2026 (Surat UIP2B Jamali No. 2153/REN.00.01/F33000000/ 2024 tanggal 22 Mei 2024)</t>
+          <t>Jangka Pendek : 1. Pembangunan proyek looping utara SUTT 150 kV Bungah- Paciran. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 3. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - 2034,COD Tahun2025, Mundur COD 2028). 4. Usulan pemasangan Kapasitor sebesar 50 MVAR di GI Petrokimia COD Tahun 2026 (Surat UIP2B Jamali No. 2153/REN.00.01/F33000000/ 2024 tanggal 22 Mei 2024)</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] TerjadiDroptegangandi Subsistem Ngimbang 1,2 terutama pada saat pekerjaan di beberapa RuasPenghantar( SUTT 150 kV Babat - Lamongan-Cerme)</t>
+          <t>[BELUM_DITETAPKAN] Terjadi Droptegangandi Subsistem Ngimbang 1,2 terutama pada saat pekerjaan di beberapa Ruas Penghantar( SUTT 150 kV Babat - Lamongan-Cerme)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3805,7 +3466,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (BerdasarkanRUPTL 2025 - 2034,CODTahun2025, MundurCOD 2028) 3. Usulan pemasangan Kapasitor sebesar 50 MVAR di GI Paciran, diperkirakan COD Tahun 2026 info UIT JBM (Surat UIP2B Jamali No. 2153/REN.00.01/F33000000/ 2024 tanggal 22 Mei 2024)</t>
+          <t>Jangka Pendek : 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - 2034,COD Tahun2025, Mundur COD 2028) 3. Usulan pemasangan Kapasitor sebesar 50 MVAR di GI Paciran, diperkirakan COD Tahun 2026 info UIT JBM (Surat UIP2B Jamali No. 2153/REN.00.01/F33000000/ 2024 tanggal 22 Mei 2024)</t>
         </is>
       </c>
     </row>
